--- a/DateBase/orders/Nhat 48_2026-5-2.xlsx
+++ b/DateBase/orders/Nhat 48_2026-5-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,34 +443,31 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>775_海芋黑_Calla Lily_undefined_1bunch</v>
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F2" t="str">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" t="str">
-        <v>788_直葱_undefined_undefined_1bunch</v>
+        <v>244_繁星_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F3" t="str">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>2</v>
-      </c>
       <c r="C4" t="str">
-        <v>615_康乃馨野马_horse_undefined_20stems</v>
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F4" t="str">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="str">
-        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+        <v>439_九星叶_undefined_undefined_1bunch</v>
       </c>
       <c r="F5" t="str">
         <v>10</v>
@@ -478,31 +475,232 @@
     </row>
     <row r="6">
       <c r="C6" t="str">
-        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
       </c>
       <c r="F6" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="str">
+        <v>2</v>
+      </c>
       <c r="C7" t="str">
-        <v>739_鸢尾花白_undefined_undefined_1bunch</v>
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
       </c>
       <c r="F7" t="str">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="str">
-        <v>738_鸢尾花蓝_undefined_undefined_1bunch</v>
+        <v>775_海芋黑_Calla Lily_undefined_1bunch</v>
       </c>
       <c r="F8" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="str">
+        <v>855_海芋粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>3</v>
+      </c>
+      <c r="C10" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F10" t="str">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F11" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>7_翠绿洋桔梗_Dark Green Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F13" t="str">
         <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>300_白星_White Gypso_ gypsophila_1kg</v>
+      </c>
+      <c r="F15" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>4</v>
+      </c>
+      <c r="C16" t="str">
+        <v>816_山里红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5</v>
+      </c>
+      <c r="C17" t="str">
+        <v>669_大丽花 红_undefined_undefined_5stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>6</v>
+      </c>
+      <c r="C19" t="str">
+        <v>356_绿枫叶山货_maple leaf small_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>356_绿枫叶山货_maple leaf small_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>326_红继木_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>432_小刺秦/情人果_small Eryngium_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="C25" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>7</v>
+      </c>
+      <c r="C27" t="str">
+        <v>770_弯葱_undefined_undefined_10stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>744_永生吊米深红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>741_袋鼠爪红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>849_婚庆卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="C31" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -557,7 +755,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>045510101015</v>
+        <v>020913105222239515154525105551055555107100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-5-2.xlsx
+++ b/DateBase/orders/Nhat 48_2026-5-2.xlsx
@@ -697,6 +697,9 @@
         <v xml:space="preserve">448_吊米 绿_hanging amaranthus
 green_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -755,7 +758,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020913105222239515154525105551055555107100</v>
+        <v>020913105222239515154525105551055555107103</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-5-2.xlsx
+++ b/DateBase/orders/Nhat 48_2026-5-2.xlsx
@@ -760,6 +760,9 @@
       <c r="G2" t="str">
         <v>020913105222239515154525105551055555107103</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
